--- a/uah_abastecimentos_3.xlsx
+++ b/uah_abastecimentos_3.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6569" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6864" uniqueCount="274">
   <si>
     <t>DATA</t>
   </si>
@@ -1118,7 +1118,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I1313"/>
+  <dimension ref="A1:I1372"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -38606,28 +38606,28 @@
         <v>46258</v>
       </c>
       <c r="B1293" s="4" t="s">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="C1293" s="4" t="s">
-        <v>199</v>
+        <v>23</v>
       </c>
       <c r="D1293" s="4">
-        <v>2968.75</v>
+        <v>704.7</v>
       </c>
       <c r="E1293" s="4">
-        <v>475</v>
+        <v>135</v>
       </c>
       <c r="F1293" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G1293" s="4">
-        <v>440205</v>
+        <v>585684</v>
       </c>
       <c r="H1293" s="4" t="s">
-        <v>208</v>
+        <v>175</v>
       </c>
       <c r="I1293" s="4" t="s">
-        <v>126</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1294" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38635,28 +38635,28 @@
         <v>46258</v>
       </c>
       <c r="B1294" s="4" t="s">
-        <v>166</v>
+        <v>218</v>
       </c>
       <c r="C1294" s="4" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D1294" s="4">
-        <v>563.01</v>
+        <v>1080.54</v>
       </c>
       <c r="E1294" s="4">
-        <v>111</v>
+        <v>207</v>
       </c>
       <c r="F1294" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G1294" s="4">
-        <v>289068</v>
+        <v>573488</v>
       </c>
       <c r="H1294" s="4" t="s">
-        <v>167</v>
+        <v>49</v>
       </c>
       <c r="I1294" s="4" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1295" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38664,28 +38664,28 @@
         <v>46258</v>
       </c>
       <c r="B1295" s="4" t="s">
-        <v>138</v>
+        <v>218</v>
       </c>
       <c r="C1295" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D1295" s="4">
-        <v>677.25</v>
+        <v>93.96</v>
       </c>
       <c r="E1295" s="4">
-        <v>129</v>
+        <v>18</v>
       </c>
       <c r="F1295" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G1295" s="4">
-        <v>571068</v>
+        <v>573549</v>
       </c>
       <c r="H1295" s="4" t="s">
-        <v>139</v>
+        <v>49</v>
       </c>
       <c r="I1295" s="4" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1296" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38693,28 +38693,28 @@
         <v>46258</v>
       </c>
       <c r="B1296" s="4" t="s">
-        <v>92</v>
+        <v>192</v>
       </c>
       <c r="C1296" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D1296" s="4">
-        <v>1207.5</v>
+        <v>1780.02</v>
       </c>
       <c r="E1296" s="4">
-        <v>230</v>
+        <v>341</v>
       </c>
       <c r="F1296" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G1296" s="4">
-        <v>92486</v>
+        <v>432140</v>
       </c>
       <c r="H1296" s="4" t="s">
-        <v>93</v>
+        <v>193</v>
       </c>
       <c r="I1296" s="4" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1297" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38722,28 +38722,28 @@
         <v>46258</v>
       </c>
       <c r="B1297" s="4" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="C1297" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D1297" s="4">
-        <v>2625</v>
+        <v>1827</v>
       </c>
       <c r="E1297" s="4">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="F1297" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G1297" s="4">
-        <v>89840</v>
+        <v>491779</v>
       </c>
       <c r="H1297" s="4" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="I1297" s="4" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1298" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38751,28 +38751,28 @@
         <v>46258</v>
       </c>
       <c r="B1298" s="4" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="C1298" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D1298" s="4">
-        <v>840</v>
+        <v>783</v>
       </c>
       <c r="E1298" s="4">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="F1298" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G1298" s="4">
-        <v>160972</v>
+        <v>481134</v>
       </c>
       <c r="H1298" s="4" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="I1298" s="4" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1299" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38780,28 +38780,28 @@
         <v>46258</v>
       </c>
       <c r="B1299" s="4" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="C1299" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D1299" s="4">
-        <v>430.5</v>
+        <v>715.14</v>
       </c>
       <c r="E1299" s="4">
-        <v>82</v>
+        <v>137</v>
       </c>
       <c r="F1299" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G1299" s="4">
-        <v>336482</v>
+        <v>131662</v>
       </c>
       <c r="H1299" s="4" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="I1299" s="4" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1300" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38809,28 +38809,28 @@
         <v>46258</v>
       </c>
       <c r="B1300" s="4" t="s">
-        <v>232</v>
+        <v>258</v>
       </c>
       <c r="C1300" s="4" t="s">
-        <v>23</v>
+        <v>109</v>
       </c>
       <c r="D1300" s="4">
-        <v>783</v>
+        <v>1786.84</v>
       </c>
       <c r="E1300" s="4">
-        <v>150</v>
+        <v>336</v>
       </c>
       <c r="F1300" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G1300" s="4">
-        <v>481134</v>
+        <v>754291</v>
       </c>
       <c r="H1300" s="4" t="s">
-        <v>233</v>
+        <v>259</v>
       </c>
       <c r="I1300" s="4" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1301" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38838,25 +38838,25 @@
         <v>46258</v>
       </c>
       <c r="B1301" s="4" t="s">
-        <v>214</v>
+        <v>257</v>
       </c>
       <c r="C1301" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D1301" s="4">
-        <v>2561.46</v>
+        <v>1754.98</v>
       </c>
       <c r="E1301" s="4">
-        <v>505</v>
+        <v>346</v>
       </c>
       <c r="F1301" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G1301" s="4">
-        <v>213936</v>
+        <v>759346</v>
       </c>
       <c r="H1301" s="4" t="s">
-        <v>215</v>
+        <v>264</v>
       </c>
       <c r="I1301" s="4" t="s">
         <v>13</v>
@@ -38867,28 +38867,28 @@
         <v>46258</v>
       </c>
       <c r="B1302" s="4" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="C1302" s="4" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D1302" s="4">
-        <v>2005.5</v>
+        <v>563.01</v>
       </c>
       <c r="E1302" s="4">
-        <v>382</v>
+        <v>111</v>
       </c>
       <c r="F1302" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G1302" s="4">
-        <v>93880</v>
+        <v>289068</v>
       </c>
       <c r="H1302" s="4" t="s">
-        <v>242</v>
+        <v>167</v>
       </c>
       <c r="I1302" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1303" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38896,25 +38896,25 @@
         <v>46258</v>
       </c>
       <c r="B1303" s="4" t="s">
-        <v>216</v>
+        <v>74</v>
       </c>
       <c r="C1303" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D1303" s="4">
-        <v>2094.8200000000002</v>
+        <v>1577.45</v>
       </c>
       <c r="E1303" s="4">
-        <v>413</v>
+        <v>311</v>
       </c>
       <c r="F1303" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G1303" s="4">
-        <v>281252</v>
+        <v>586096</v>
       </c>
       <c r="H1303" s="4" t="s">
-        <v>217</v>
+        <v>159</v>
       </c>
       <c r="I1303" s="4" t="s">
         <v>13</v>
@@ -38925,25 +38925,25 @@
         <v>46258</v>
       </c>
       <c r="B1304" s="4" t="s">
-        <v>115</v>
+        <v>216</v>
       </c>
       <c r="C1304" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D1304" s="4">
-        <v>2470.16</v>
+        <v>2094.8200000000002</v>
       </c>
       <c r="E1304" s="4">
-        <v>487</v>
+        <v>413</v>
       </c>
       <c r="F1304" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G1304" s="4">
-        <v>229759</v>
+        <v>281252</v>
       </c>
       <c r="H1304" s="4" t="s">
-        <v>116</v>
+        <v>217</v>
       </c>
       <c r="I1304" s="4" t="s">
         <v>13</v>
@@ -38954,28 +38954,28 @@
         <v>46258</v>
       </c>
       <c r="B1305" s="4" t="s">
-        <v>62</v>
+        <v>214</v>
       </c>
       <c r="C1305" s="4" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D1305" s="4">
-        <v>467.25</v>
+        <v>2561.46</v>
       </c>
       <c r="E1305" s="4">
-        <v>89</v>
+        <v>505</v>
       </c>
       <c r="F1305" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G1305" s="4">
-        <v>388635</v>
+        <v>213936</v>
       </c>
       <c r="H1305" s="4" t="s">
-        <v>63</v>
+        <v>215</v>
       </c>
       <c r="I1305" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1306" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38983,28 +38983,28 @@
         <v>46258</v>
       </c>
       <c r="B1306" s="4" t="s">
-        <v>66</v>
+        <v>115</v>
       </c>
       <c r="C1306" s="4" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D1306" s="4">
-        <v>504</v>
+        <v>2470.16</v>
       </c>
       <c r="E1306" s="4">
-        <v>96</v>
+        <v>487</v>
       </c>
       <c r="F1306" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G1306" s="4">
-        <v>728673</v>
+        <v>229759</v>
       </c>
       <c r="H1306" s="4" t="s">
-        <v>67</v>
+        <v>116</v>
       </c>
       <c r="I1306" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1307" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39012,28 +39012,28 @@
         <v>46258</v>
       </c>
       <c r="B1307" s="4" t="s">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="C1307" s="4" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D1307" s="4">
-        <v>1577.45</v>
+        <v>2495.4299999999998</v>
       </c>
       <c r="E1307" s="4">
-        <v>311</v>
+        <v>373.01</v>
       </c>
       <c r="F1307" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G1307" s="4">
-        <v>586096</v>
+        <v>410375</v>
       </c>
       <c r="H1307" s="4" t="s">
-        <v>159</v>
+        <v>131</v>
       </c>
       <c r="I1307" s="4" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1308" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39041,28 +39041,28 @@
         <v>46258</v>
       </c>
       <c r="B1308" s="4" t="s">
-        <v>257</v>
+        <v>207</v>
       </c>
       <c r="C1308" s="4" t="s">
-        <v>10</v>
+        <v>199</v>
       </c>
       <c r="D1308" s="4">
-        <v>1754.98</v>
+        <v>2968.75</v>
       </c>
       <c r="E1308" s="4">
-        <v>346</v>
+        <v>475</v>
       </c>
       <c r="F1308" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G1308" s="4">
-        <v>759346</v>
+        <v>440205</v>
       </c>
       <c r="H1308" s="4" t="s">
-        <v>264</v>
+        <v>208</v>
       </c>
       <c r="I1308" s="4" t="s">
-        <v>13</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1309" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39099,28 +39099,28 @@
         <v>46258</v>
       </c>
       <c r="B1310" s="4" t="s">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="C1310" s="4" t="s">
-        <v>19</v>
+        <v>256</v>
       </c>
       <c r="D1310" s="4">
-        <v>2495.4299999999998</v>
+        <v>682.13</v>
       </c>
       <c r="E1310" s="4">
-        <v>373.01</v>
+        <v>108.44</v>
       </c>
       <c r="F1310" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G1310" s="4">
-        <v>410375</v>
+        <v>563501</v>
       </c>
       <c r="H1310" s="4" t="s">
-        <v>131</v>
+        <v>85</v>
       </c>
       <c r="I1310" s="4" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
     </row>
     <row r="1311" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39128,28 +39128,28 @@
         <v>46258</v>
       </c>
       <c r="B1311" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C1311" s="4" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="D1311" s="4">
-        <v>715.14</v>
+        <v>961.11</v>
       </c>
       <c r="E1311" s="4">
-        <v>137</v>
+        <v>143.66499999999999</v>
       </c>
       <c r="F1311" s="4" t="s">
-        <v>11</v>
+        <v>246</v>
       </c>
       <c r="G1311" s="4">
-        <v>131662</v>
+        <v>757852</v>
       </c>
       <c r="H1311" s="4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I1311" s="4" t="s">
-        <v>25</v>
+        <v>83</v>
       </c>
     </row>
     <row r="1312" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39157,25 +39157,25 @@
         <v>46258</v>
       </c>
       <c r="B1312" s="4" t="s">
-        <v>80</v>
+        <v>237</v>
       </c>
       <c r="C1312" s="4" t="s">
         <v>81</v>
       </c>
       <c r="D1312" s="4">
-        <v>961.11</v>
+        <v>1682.24</v>
       </c>
       <c r="E1312" s="4">
-        <v>143.66499999999999</v>
+        <v>240.66499999999999</v>
       </c>
       <c r="F1312" s="4" t="s">
-        <v>246</v>
+        <v>11</v>
       </c>
       <c r="G1312" s="4">
-        <v>757852</v>
+        <v>497289</v>
       </c>
       <c r="H1312" s="4" t="s">
-        <v>82</v>
+        <v>238</v>
       </c>
       <c r="I1312" s="4" t="s">
         <v>83</v>
@@ -39186,36 +39186,1743 @@
         <v>46258</v>
       </c>
       <c r="B1313" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C1313" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1313" s="4">
+        <v>843.6</v>
+      </c>
+      <c r="E1313" s="4">
+        <v>128.01300000000001</v>
+      </c>
+      <c r="F1313" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1313" s="4">
+        <v>430194</v>
+      </c>
+      <c r="H1313" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1313" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1314" s="3">
+        <v>46258</v>
+      </c>
+      <c r="B1314" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C1314" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1314" s="4">
+        <v>1207.5</v>
+      </c>
+      <c r="E1314" s="4">
+        <v>230</v>
+      </c>
+      <c r="F1314" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1314" s="4">
+        <v>869131</v>
+      </c>
+      <c r="H1314" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="I1314" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1315" s="3">
+        <v>46258</v>
+      </c>
+      <c r="B1315" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1315" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1315" s="4">
+        <v>677.25</v>
+      </c>
+      <c r="E1315" s="4">
+        <v>129</v>
+      </c>
+      <c r="F1315" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1315" s="4">
+        <v>571068</v>
+      </c>
+      <c r="H1315" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="I1315" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1316" s="3">
+        <v>46258</v>
+      </c>
+      <c r="B1316" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1316" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1316" s="4">
+        <v>698.25</v>
+      </c>
+      <c r="E1316" s="4">
+        <v>133</v>
+      </c>
+      <c r="F1316" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1316" s="4">
+        <v>783792</v>
+      </c>
+      <c r="H1316" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1316" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1317" s="3">
+        <v>46258</v>
+      </c>
+      <c r="B1317" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C1317" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1317" s="4">
+        <v>430.5</v>
+      </c>
+      <c r="E1317" s="4">
+        <v>82</v>
+      </c>
+      <c r="F1317" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1317" s="4">
+        <v>336482</v>
+      </c>
+      <c r="H1317" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I1317" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1318" s="3">
+        <v>46258</v>
+      </c>
+      <c r="B1318" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C1318" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1318" s="4">
+        <v>913.5</v>
+      </c>
+      <c r="E1318" s="4">
+        <v>174</v>
+      </c>
+      <c r="F1318" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1318" s="4">
+        <v>401509</v>
+      </c>
+      <c r="H1318" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="I1318" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1319" s="3">
+        <v>46258</v>
+      </c>
+      <c r="B1319" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1319" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1319" s="4">
+        <v>2467.5</v>
+      </c>
+      <c r="E1319" s="4">
+        <v>470</v>
+      </c>
+      <c r="F1319" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1319" s="4">
+        <v>402444</v>
+      </c>
+      <c r="H1319" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="I1319" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1320" s="3">
+        <v>46258</v>
+      </c>
+      <c r="B1320" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1320" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1320" s="4">
+        <v>504</v>
+      </c>
+      <c r="E1320" s="4">
+        <v>96</v>
+      </c>
+      <c r="F1320" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1320" s="4">
+        <v>728673</v>
+      </c>
+      <c r="H1320" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1320" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1321" s="3">
+        <v>46258</v>
+      </c>
+      <c r="B1321" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1321" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1321" s="4">
+        <v>467.25</v>
+      </c>
+      <c r="E1321" s="4">
+        <v>89</v>
+      </c>
+      <c r="F1321" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1321" s="4">
+        <v>388635</v>
+      </c>
+      <c r="H1321" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1321" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1322" s="3">
+        <v>46258</v>
+      </c>
+      <c r="B1322" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C1322" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1322" s="4">
+        <v>840</v>
+      </c>
+      <c r="E1322" s="4">
+        <v>160</v>
+      </c>
+      <c r="F1322" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1322" s="4">
+        <v>160972</v>
+      </c>
+      <c r="H1322" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="I1322" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1323" s="3">
+        <v>46258</v>
+      </c>
+      <c r="B1323" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1323" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1323" s="4">
+        <v>1207.5</v>
+      </c>
+      <c r="E1323" s="4">
+        <v>230</v>
+      </c>
+      <c r="F1323" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1323" s="4">
+        <v>92486</v>
+      </c>
+      <c r="H1323" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I1323" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1324" s="3">
+        <v>46258</v>
+      </c>
+      <c r="B1324" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C1324" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1324" s="4">
+        <v>2625</v>
+      </c>
+      <c r="E1324" s="4">
+        <v>500</v>
+      </c>
+      <c r="F1324" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1324" s="4">
+        <v>89840</v>
+      </c>
+      <c r="H1324" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I1324" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1325" s="3">
+        <v>46258</v>
+      </c>
+      <c r="B1325" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1325" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1325" s="4">
+        <v>2005.5</v>
+      </c>
+      <c r="E1325" s="4">
+        <v>382</v>
+      </c>
+      <c r="F1325" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1325" s="4">
+        <v>93880</v>
+      </c>
+      <c r="H1325" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="I1325" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1326" s="3">
+        <v>46258</v>
+      </c>
+      <c r="B1326" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C1326" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1326" s="4">
+        <v>756</v>
+      </c>
+      <c r="E1326" s="4">
+        <v>144</v>
+      </c>
+      <c r="F1326" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1326" s="4">
+        <v>37925</v>
+      </c>
+      <c r="H1326" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="I1326" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1327" s="3">
+        <v>46258</v>
+      </c>
+      <c r="B1327" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C1313" s="4" t="s">
+      <c r="C1327" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D1313" s="4">
+      <c r="D1327" s="4">
         <v>1102.5</v>
       </c>
-      <c r="E1313" s="4">
+      <c r="E1327" s="4">
         <v>210</v>
       </c>
-      <c r="F1313" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1313" s="4">
+      <c r="F1327" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1327" s="4">
         <v>14786</v>
       </c>
-      <c r="H1313" s="4" t="s">
+      <c r="H1327" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="I1313" s="4" t="s">
+      <c r="I1327" s="4" t="s">
         <v>17</v>
       </c>
     </row>
+    <row r="1328" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1328" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1328" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C1328" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1328" s="4">
+        <v>590.19000000000005</v>
+      </c>
+      <c r="E1328" s="4">
+        <v>113</v>
+      </c>
+      <c r="F1328" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1328" s="4">
+        <v>576233</v>
+      </c>
+      <c r="H1328" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="I1328" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1329" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1329" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1329" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1329" s="4">
+        <v>271.58999999999997</v>
+      </c>
+      <c r="E1329" s="4">
+        <v>52</v>
+      </c>
+      <c r="F1329" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1329" s="4">
+        <v>924822</v>
+      </c>
+      <c r="H1329" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1329" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1330" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1330" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C1330" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1330" s="4">
+        <v>903.57</v>
+      </c>
+      <c r="E1330" s="4">
+        <v>173</v>
+      </c>
+      <c r="F1330" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1330" s="4">
+        <v>398921</v>
+      </c>
+      <c r="H1330" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="I1330" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1331" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1331" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1331" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1331" s="4">
+        <v>720.77</v>
+      </c>
+      <c r="E1331" s="4">
+        <v>138</v>
+      </c>
+      <c r="F1331" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1331" s="4">
+        <v>459167</v>
+      </c>
+      <c r="H1331" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="I1331" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1332" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1332" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1332" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1332" s="4">
+        <v>1310.97</v>
+      </c>
+      <c r="E1332" s="4">
+        <v>251</v>
+      </c>
+      <c r="F1332" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1332" s="4">
+        <v>509582</v>
+      </c>
+      <c r="H1332" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1332" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1333" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1333" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="C1333" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1333" s="4">
+        <v>1008.39</v>
+      </c>
+      <c r="E1333" s="4">
+        <v>193</v>
+      </c>
+      <c r="F1333" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1333" s="4">
+        <v>686116</v>
+      </c>
+      <c r="H1333" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="I1333" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1334" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1334" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1334" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1334" s="4">
+        <v>1582.56</v>
+      </c>
+      <c r="E1334" s="4">
+        <v>303</v>
+      </c>
+      <c r="F1334" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1334" s="4">
+        <v>452338</v>
+      </c>
+      <c r="H1334" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="I1334" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1335" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1335" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C1335" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1335" s="4">
+        <v>1440.72</v>
+      </c>
+      <c r="E1335" s="4">
+        <v>276</v>
+      </c>
+      <c r="F1335" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1335" s="4">
+        <v>133664</v>
+      </c>
+      <c r="H1335" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="I1335" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1336" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1336" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1336" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1336" s="4">
+        <v>626.76</v>
+      </c>
+      <c r="E1336" s="4">
+        <v>120</v>
+      </c>
+      <c r="F1336" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1336" s="4">
+        <v>132009</v>
+      </c>
+      <c r="H1336" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1336" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1337" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1337" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="C1337" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1337" s="4">
+        <v>1074.24</v>
+      </c>
+      <c r="E1337" s="4">
+        <v>202.00200000000001</v>
+      </c>
+      <c r="F1337" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1337" s="4">
+        <v>754952</v>
+      </c>
+      <c r="H1337" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="I1337" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1338" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1338" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1338" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1338" s="4">
+        <v>1998.44</v>
+      </c>
+      <c r="E1338" s="4">
+        <v>394</v>
+      </c>
+      <c r="F1338" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1338" s="4">
+        <v>747829</v>
+      </c>
+      <c r="H1338" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="I1338" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1339" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1339" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C1339" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1339" s="4">
+        <v>1836.13</v>
+      </c>
+      <c r="E1339" s="4">
+        <v>362</v>
+      </c>
+      <c r="F1339" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1339" s="4">
+        <v>736018</v>
+      </c>
+      <c r="H1339" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="I1339" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1340" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1340" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1340" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1340" s="4">
+        <v>2693.33</v>
+      </c>
+      <c r="E1340" s="4">
+        <v>531</v>
+      </c>
+      <c r="F1340" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1340" s="4">
+        <v>604436</v>
+      </c>
+      <c r="H1340" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="I1340" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1341" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1341" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C1341" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1341" s="4">
+        <v>1679.4</v>
+      </c>
+      <c r="E1341" s="4">
+        <v>331</v>
+      </c>
+      <c r="F1341" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1341" s="4">
+        <v>625430</v>
+      </c>
+      <c r="H1341" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="I1341" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1342" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1342" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C1342" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1342" s="4">
+        <v>1983.23</v>
+      </c>
+      <c r="E1342" s="4">
+        <v>391</v>
+      </c>
+      <c r="F1342" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1342" s="4">
+        <v>624969</v>
+      </c>
+      <c r="H1342" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I1342" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1343" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1343" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C1343" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1343" s="4">
+        <v>1678.9</v>
+      </c>
+      <c r="E1343" s="4">
+        <v>331</v>
+      </c>
+      <c r="F1343" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1343" s="4">
+        <v>580221</v>
+      </c>
+      <c r="H1343" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="I1343" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1344" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1344" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1344" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1344" s="4">
+        <v>1562.24</v>
+      </c>
+      <c r="E1344" s="4">
+        <v>308</v>
+      </c>
+      <c r="F1344" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1344" s="4">
+        <v>300452</v>
+      </c>
+      <c r="H1344" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="I1344" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1345" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1345" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1345" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1345" s="4">
+        <v>1780.34</v>
+      </c>
+      <c r="E1345" s="4">
+        <v>351</v>
+      </c>
+      <c r="F1345" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1345" s="4">
+        <v>283550</v>
+      </c>
+      <c r="H1345" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1345" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1346" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1346" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C1346" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1346" s="4">
+        <v>1806.58</v>
+      </c>
+      <c r="E1346" s="4">
+        <v>356</v>
+      </c>
+      <c r="F1346" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1346" s="4">
+        <v>261662</v>
+      </c>
+      <c r="H1346" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="I1346" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1347" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1347" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1347" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1347" s="4">
+        <v>2738.98</v>
+      </c>
+      <c r="E1347" s="4">
+        <v>540</v>
+      </c>
+      <c r="F1347" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1347" s="4">
+        <v>268279</v>
+      </c>
+      <c r="H1347" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1347" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1348" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1348" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C1348" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1348" s="4">
+        <v>1374.56</v>
+      </c>
+      <c r="E1348" s="4">
+        <v>271</v>
+      </c>
+      <c r="F1348" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1348" s="4">
+        <v>281913</v>
+      </c>
+      <c r="H1348" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="I1348" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1349" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1349" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1349" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1349" s="4">
+        <v>2389</v>
+      </c>
+      <c r="E1349" s="4">
+        <v>471</v>
+      </c>
+      <c r="F1349" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1349" s="4">
+        <v>225066</v>
+      </c>
+      <c r="H1349" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="I1349" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1350" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1350" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C1350" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1350" s="4">
+        <v>2237.52</v>
+      </c>
+      <c r="E1350" s="4">
+        <v>441</v>
+      </c>
+      <c r="F1350" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1350" s="4">
+        <v>96914</v>
+      </c>
+      <c r="H1350" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="I1350" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1351" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1351" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1351" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1351" s="4">
+        <v>1521.66</v>
+      </c>
+      <c r="E1351" s="4">
+        <v>300</v>
+      </c>
+      <c r="F1351" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1351" s="4">
+        <v>97425</v>
+      </c>
+      <c r="H1351" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="I1351" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1352" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1352" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1352" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1352" s="4">
+        <v>1765.12</v>
+      </c>
+      <c r="E1352" s="4">
+        <v>348</v>
+      </c>
+      <c r="F1352" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1352" s="4">
+        <v>98122</v>
+      </c>
+      <c r="H1352" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="I1352" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1353" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1353" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1353" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1353" s="4">
+        <v>1699.18</v>
+      </c>
+      <c r="E1353" s="4">
+        <v>335</v>
+      </c>
+      <c r="F1353" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1353" s="4">
+        <v>101957</v>
+      </c>
+      <c r="H1353" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1353" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1354" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1354" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="C1354" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1354" s="4">
+        <v>2130.3200000000002</v>
+      </c>
+      <c r="E1354" s="4">
+        <v>420</v>
+      </c>
+      <c r="F1354" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1354" s="4">
+        <v>93839</v>
+      </c>
+      <c r="H1354" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="I1354" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1355" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1355" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1355" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1355" s="4">
+        <v>1018.04</v>
+      </c>
+      <c r="E1355" s="4">
+        <v>172.17400000000001</v>
+      </c>
+      <c r="F1355" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1355" s="4">
+        <v>388716</v>
+      </c>
+      <c r="H1355" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1355" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1356" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1356" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C1356" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D1356" s="4">
+        <v>2340.25</v>
+      </c>
+      <c r="E1356" s="4">
+        <v>374.44</v>
+      </c>
+      <c r="F1356" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1356" s="4">
+        <v>379943</v>
+      </c>
+      <c r="H1356" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="I1356" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1357" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1357" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C1357" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1357" s="4">
+        <v>1713.4</v>
+      </c>
+      <c r="E1357" s="4">
+        <v>260</v>
+      </c>
+      <c r="F1357" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1357" s="4">
+        <v>386082</v>
+      </c>
+      <c r="H1357" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="I1357" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1358" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1358" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="C1358" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1358" s="4">
+        <v>1383.9</v>
+      </c>
+      <c r="E1358" s="4">
+        <v>210</v>
+      </c>
+      <c r="F1358" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1358" s="4">
+        <v>370734</v>
+      </c>
+      <c r="H1358" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="I1358" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1359" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1359" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1359" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1359" s="4">
+        <v>1785.89</v>
+      </c>
+      <c r="E1359" s="4">
+        <v>271</v>
+      </c>
+      <c r="F1359" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1359" s="4">
+        <v>446938</v>
+      </c>
+      <c r="H1359" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1359" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1360" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1360" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C1360" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1360" s="4">
+        <v>1469.96</v>
+      </c>
+      <c r="E1360" s="4">
+        <v>210.29499999999999</v>
+      </c>
+      <c r="F1360" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1360" s="4">
+        <v>477926</v>
+      </c>
+      <c r="H1360" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="I1360" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1361" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1361" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1361" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1361" s="4">
+        <v>1318.03</v>
+      </c>
+      <c r="E1361" s="4">
+        <v>200.005</v>
+      </c>
+      <c r="F1361" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1361" s="4">
+        <v>423914</v>
+      </c>
+      <c r="H1361" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1361" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1362" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1362" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C1362" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1362" s="4">
+        <v>378</v>
+      </c>
+      <c r="E1362" s="4">
+        <v>72</v>
+      </c>
+      <c r="F1362" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1362" s="4">
+        <v>869399</v>
+      </c>
+      <c r="H1362" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="I1362" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1363" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1363" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1363" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1363" s="4">
+        <v>540.75</v>
+      </c>
+      <c r="E1363" s="4">
+        <v>103</v>
+      </c>
+      <c r="F1363" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1363" s="4">
+        <v>784154</v>
+      </c>
+      <c r="H1363" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1363" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1364" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1364" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C1364" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1364" s="4">
+        <v>525</v>
+      </c>
+      <c r="E1364" s="4">
+        <v>100</v>
+      </c>
+      <c r="F1364" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1364" s="4">
+        <v>336839</v>
+      </c>
+      <c r="H1364" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I1364" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1365" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1365" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1365" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1365" s="4">
+        <v>614.25</v>
+      </c>
+      <c r="E1365" s="4">
+        <v>117</v>
+      </c>
+      <c r="F1365" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1365" s="4">
+        <v>729120</v>
+      </c>
+      <c r="H1365" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1365" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1366" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1366" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1366" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1366" s="4">
+        <v>997.5</v>
+      </c>
+      <c r="E1366" s="4">
+        <v>190</v>
+      </c>
+      <c r="F1366" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1366" s="4">
+        <v>750710</v>
+      </c>
+      <c r="H1366" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="I1366" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1367" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1367" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1367" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1367" s="4">
+        <v>609</v>
+      </c>
+      <c r="E1367" s="4">
+        <v>116</v>
+      </c>
+      <c r="F1367" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1367" s="4">
+        <v>685216</v>
+      </c>
+      <c r="H1367" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I1367" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1368" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1368" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C1368" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1368" s="4">
+        <v>1123.5</v>
+      </c>
+      <c r="E1368" s="4">
+        <v>214</v>
+      </c>
+      <c r="F1368" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1368" s="4">
+        <v>604160</v>
+      </c>
+      <c r="H1368" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="I1368" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1369" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1369" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1369" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1369" s="4">
+        <v>399</v>
+      </c>
+      <c r="E1369" s="4">
+        <v>76</v>
+      </c>
+      <c r="F1369" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1369" s="4">
+        <v>156020</v>
+      </c>
+      <c r="H1369" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1369" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1370" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1370" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1370" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1370" s="4">
+        <v>563</v>
+      </c>
+      <c r="E1370" s="4">
+        <v>120</v>
+      </c>
+      <c r="F1370" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1370" s="4">
+        <v>15245</v>
+      </c>
+      <c r="H1370" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="I1370" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1371" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1371" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C1371" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="D1371" s="4">
+        <v>715.68</v>
+      </c>
+      <c r="E1371" s="4">
+        <v>112</v>
+      </c>
+      <c r="F1371" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1371" s="4">
+        <v>370955</v>
+      </c>
+      <c r="H1371" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="I1371" s="4" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1372" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B1372" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1372" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1372" s="4">
+        <v>959.95</v>
+      </c>
+      <c r="E1372" s="4">
+        <v>180.51</v>
+      </c>
+      <c r="F1372" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1372" s="4">
+        <v>527133</v>
+      </c>
+      <c r="H1372" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1372" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1252">
-    <sortState ref="A2:I1090">
-      <sortCondition ref="A1:A1037"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:I1252"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>

--- a/uah_abastecimentos_3.xlsx
+++ b/uah_abastecimentos_3.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6859" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7044" uniqueCount="271">
   <si>
     <t>DATA</t>
   </si>
@@ -1109,7 +1109,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I1371"/>
+  <dimension ref="A1:I1408"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -40883,6 +40883,1079 @@
         <v>111</v>
       </c>
     </row>
+    <row r="1372" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1372" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B1372" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C1372" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1372" s="4">
+        <v>811.8</v>
+      </c>
+      <c r="E1372" s="4">
+        <v>160</v>
+      </c>
+      <c r="F1372" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1372" s="4">
+        <v>289644</v>
+      </c>
+      <c r="H1372" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="I1372" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1373" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B1373" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1373" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1373" s="4">
+        <v>761.25</v>
+      </c>
+      <c r="E1373" s="4">
+        <v>145</v>
+      </c>
+      <c r="F1373" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1373" s="4">
+        <v>571676</v>
+      </c>
+      <c r="H1373" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="I1373" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1374" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B1374" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C1374" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1374" s="4">
+        <v>777</v>
+      </c>
+      <c r="E1374" s="4">
+        <v>148</v>
+      </c>
+      <c r="F1374" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1374" s="4">
+        <v>401769</v>
+      </c>
+      <c r="H1374" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="I1374" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1375" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B1375" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="C1375" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1375" s="4">
+        <v>526.61</v>
+      </c>
+      <c r="E1375" s="4">
+        <v>101</v>
+      </c>
+      <c r="F1375" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1375" s="4">
+        <v>712982</v>
+      </c>
+      <c r="H1375" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1375" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1376" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B1376" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C1376" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1376" s="4">
+        <v>1366.06</v>
+      </c>
+      <c r="E1376" s="4">
+        <v>262</v>
+      </c>
+      <c r="F1376" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1376" s="4">
+        <v>461270</v>
+      </c>
+      <c r="H1376" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="I1376" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1377" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B1377" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C1377" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1377" s="4">
+        <v>1496.75</v>
+      </c>
+      <c r="E1377" s="4">
+        <v>295</v>
+      </c>
+      <c r="F1377" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1377" s="4">
+        <v>96993</v>
+      </c>
+      <c r="H1377" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="I1377" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1378" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B1378" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1378" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1378" s="4">
+        <v>2744.89</v>
+      </c>
+      <c r="E1378" s="4">
+        <v>541</v>
+      </c>
+      <c r="F1378" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1378" s="4">
+        <v>576042</v>
+      </c>
+      <c r="H1378" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1378" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1379" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B1379" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1379" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1379" s="4">
+        <v>1781.67</v>
+      </c>
+      <c r="E1379" s="4">
+        <v>351</v>
+      </c>
+      <c r="F1379" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1379" s="4">
+        <v>298711</v>
+      </c>
+      <c r="H1379" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I1379" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1380" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B1380" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C1380" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1380" s="4">
+        <v>2536.87</v>
+      </c>
+      <c r="E1380" s="4">
+        <v>500</v>
+      </c>
+      <c r="F1380" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1380" s="4">
+        <v>772858</v>
+      </c>
+      <c r="H1380" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="I1380" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1381" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B1381" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="C1381" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1381" s="4">
+        <v>1579.84</v>
+      </c>
+      <c r="E1381" s="4">
+        <v>303</v>
+      </c>
+      <c r="F1381" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1381" s="4">
+        <v>118718</v>
+      </c>
+      <c r="H1381" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="I1381" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1382" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B1382" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C1382" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1382" s="4">
+        <v>640.5</v>
+      </c>
+      <c r="E1382" s="4">
+        <v>122</v>
+      </c>
+      <c r="F1382" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1382" s="4">
+        <v>38346</v>
+      </c>
+      <c r="H1382" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="I1382" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1383" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B1383" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C1383" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1383" s="4">
+        <v>1506</v>
+      </c>
+      <c r="E1383" s="4">
+        <v>286.86</v>
+      </c>
+      <c r="F1383" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1383" s="4">
+        <v>19100</v>
+      </c>
+      <c r="H1383" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="I1383" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1384" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B1384" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C1384" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1384" s="4">
+        <v>1679.4</v>
+      </c>
+      <c r="E1384" s="4">
+        <v>331</v>
+      </c>
+      <c r="F1384" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1384" s="4">
+        <v>214895</v>
+      </c>
+      <c r="H1384" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="I1384" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1385" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B1385" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C1385" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1385" s="4">
+        <v>1770.73</v>
+      </c>
+      <c r="E1385" s="4">
+        <v>349</v>
+      </c>
+      <c r="F1385" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1385" s="4">
+        <v>282095</v>
+      </c>
+      <c r="H1385" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="I1385" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1386" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B1386" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1386" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1386" s="4">
+        <v>693</v>
+      </c>
+      <c r="E1386" s="4">
+        <v>132</v>
+      </c>
+      <c r="F1386" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1386" s="4">
+        <v>398785</v>
+      </c>
+      <c r="H1386" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I1386" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1387" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B1387" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C1387" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1387" s="4">
+        <v>1653.75</v>
+      </c>
+      <c r="E1387" s="4">
+        <v>315</v>
+      </c>
+      <c r="F1387" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1387" s="4">
+        <v>495326</v>
+      </c>
+      <c r="H1387" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I1387" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1388" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B1388" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C1388" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1388" s="4">
+        <v>636.1</v>
+      </c>
+      <c r="E1388" s="4">
+        <v>122</v>
+      </c>
+      <c r="F1388" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1388" s="4">
+        <v>399151</v>
+      </c>
+      <c r="H1388" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="I1388" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1389" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B1389" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C1389" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1389" s="4">
+        <v>1232.48</v>
+      </c>
+      <c r="E1389" s="4">
+        <v>187.023</v>
+      </c>
+      <c r="F1389" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1389" s="4">
+        <v>430301</v>
+      </c>
+      <c r="H1389" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1389" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1390" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B1390" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C1390" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1390" s="4">
+        <v>1149.75</v>
+      </c>
+      <c r="E1390" s="4">
+        <v>219</v>
+      </c>
+      <c r="F1390" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1390" s="4">
+        <v>413809</v>
+      </c>
+      <c r="H1390" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="I1390" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1391" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B1391" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1391" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D1391" s="4">
+        <v>806.22</v>
+      </c>
+      <c r="E1391" s="4">
+        <v>122.34</v>
+      </c>
+      <c r="F1391" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1391" s="4">
+        <v>416617</v>
+      </c>
+      <c r="H1391" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="I1391" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1392" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B1392" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1392" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1392" s="4">
+        <v>519.75</v>
+      </c>
+      <c r="E1392" s="4">
+        <v>99</v>
+      </c>
+      <c r="F1392" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1392" s="4">
+        <v>389035</v>
+      </c>
+      <c r="H1392" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1392" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1393" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B1393" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C1393" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1393" s="4">
+        <v>672</v>
+      </c>
+      <c r="E1393" s="4">
+        <v>128</v>
+      </c>
+      <c r="F1393" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1393" s="4">
+        <v>495578</v>
+      </c>
+      <c r="H1393" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="I1393" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1394" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B1394" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1394" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1394" s="4">
+        <v>1761.36</v>
+      </c>
+      <c r="E1394" s="4">
+        <v>347</v>
+      </c>
+      <c r="F1394" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1394" s="4">
+        <v>748395</v>
+      </c>
+      <c r="H1394" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="I1394" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1395" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B1395" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C1395" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1395" s="4">
+        <v>1680.15</v>
+      </c>
+      <c r="E1395" s="4">
+        <v>331</v>
+      </c>
+      <c r="F1395" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1395" s="4">
+        <v>735028</v>
+      </c>
+      <c r="H1395" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="I1395" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1396" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B1396" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C1396" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1396" s="4">
+        <v>995.87</v>
+      </c>
+      <c r="E1396" s="4">
+        <v>191</v>
+      </c>
+      <c r="F1396" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1396" s="4">
+        <v>134124</v>
+      </c>
+      <c r="H1396" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="I1396" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1397" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B1397" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1397" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1397" s="4">
+        <v>357</v>
+      </c>
+      <c r="E1397" s="4">
+        <v>68</v>
+      </c>
+      <c r="F1397" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1397" s="4">
+        <v>729340</v>
+      </c>
+      <c r="H1397" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1397" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1398" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B1398" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1398" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="D1398" s="4">
+        <v>666.2</v>
+      </c>
+      <c r="E1398" s="4">
+        <v>105.914</v>
+      </c>
+      <c r="F1398" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1398" s="4">
+        <v>573400</v>
+      </c>
+      <c r="H1398" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1398" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1399" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B1399" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1399" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1399" s="4">
+        <v>703.89</v>
+      </c>
+      <c r="E1399" s="4">
+        <v>135</v>
+      </c>
+      <c r="F1399" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1399" s="4">
+        <v>432378</v>
+      </c>
+      <c r="H1399" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="I1399" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1400" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B1400" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1400" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1400" s="4">
+        <v>2350.17</v>
+      </c>
+      <c r="E1400" s="4">
+        <v>463</v>
+      </c>
+      <c r="F1400" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1400" s="4">
+        <v>770589</v>
+      </c>
+      <c r="H1400" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="I1400" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1401" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B1401" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="C1401" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1401" s="4">
+        <v>1579.84</v>
+      </c>
+      <c r="E1401" s="4">
+        <v>303</v>
+      </c>
+      <c r="F1401" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1401" s="4">
+        <v>463651</v>
+      </c>
+      <c r="H1401" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="I1401" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1402" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B1402" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1402" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="D1402" s="4">
+        <v>753.2</v>
+      </c>
+      <c r="E1402" s="4">
+        <v>119.75</v>
+      </c>
+      <c r="F1402" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1402" s="4">
+        <v>563850</v>
+      </c>
+      <c r="H1402" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I1402" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1403" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B1403" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="C1403" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1403" s="4">
+        <v>286.77</v>
+      </c>
+      <c r="E1403" s="4">
+        <v>55</v>
+      </c>
+      <c r="F1403" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1403" s="4">
+        <v>686322</v>
+      </c>
+      <c r="H1403" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="I1403" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1404" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B1404" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C1404" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1404" s="4">
+        <v>646.53</v>
+      </c>
+      <c r="E1404" s="4">
+        <v>124</v>
+      </c>
+      <c r="F1404" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1404" s="4">
+        <v>492005</v>
+      </c>
+      <c r="H1404" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="I1404" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1405" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B1405" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C1405" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1405" s="4">
+        <v>2817.16</v>
+      </c>
+      <c r="E1405" s="4">
+        <v>555</v>
+      </c>
+      <c r="F1405" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1405" s="4">
+        <v>599011</v>
+      </c>
+      <c r="H1405" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="I1405" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1406" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B1406" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1406" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1406" s="4">
+        <v>2075.17</v>
+      </c>
+      <c r="E1406" s="4">
+        <v>398</v>
+      </c>
+      <c r="F1406" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1406" s="4">
+        <v>472664</v>
+      </c>
+      <c r="H1406" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1406" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1407" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B1407" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1407" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1407" s="4">
+        <v>630</v>
+      </c>
+      <c r="E1407" s="4">
+        <v>120</v>
+      </c>
+      <c r="F1407" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1407" s="4">
+        <v>15245</v>
+      </c>
+      <c r="H1407" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="I1407" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1408" s="3">
+        <v>46261</v>
+      </c>
+      <c r="B1408" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1408" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1408" s="4">
+        <v>1160.25</v>
+      </c>
+      <c r="E1408" s="4">
+        <v>221</v>
+      </c>
+      <c r="F1408" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1408" s="4">
+        <v>414977</v>
+      </c>
+      <c r="H1408" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="I1408" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1371"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
